--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488104_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488104_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2394</v>
+        <v>11.7599</v>
       </c>
       <c r="E2" t="n">
-        <v>9.804399999999999</v>
+        <v>10.1954</v>
       </c>
       <c r="F2" t="n">
-        <v>2.435</v>
+        <v>1.5645</v>
       </c>
       <c r="G2" t="n">
         <v>10.979</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2365</v>
+        <v>0.757</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7157</v>
+        <v>-0.3247</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9521</v>
+        <v>1.0817</v>
       </c>
       <c r="V2" t="n">
         <v>-2.7512</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9347</v>
+        <v>5.9619</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6972</v>
+        <v>2.7244</v>
       </c>
       <c r="F3" t="n">
         <v>3.2375</v>
@@ -688,10 +688,10 @@
         <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7437</v>
+        <v>0.7708</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3217</v>
+        <v>0.3489</v>
       </c>
       <c r="U3" t="n">
         <v>0.422</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7715</v>
+        <v>5.7912</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0876</v>
+        <v>6.4162</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3161</v>
+        <v>-0.625</v>
       </c>
       <c r="G4" t="n">
         <v>4.9652</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.73</v>
+        <v>0.7497</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2275</v>
+        <v>0.101</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9576</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.6709000000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.016</v>
+        <v>3.1081</v>
       </c>
       <c r="E5" t="n">
-        <v>3.016</v>
+        <v>2.2018</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.9062</v>
       </c>
       <c r="G5" t="n">
-        <v>3.016</v>
+        <v>1.6508</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.5512</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4107</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.016</v>
+        <v>3.5003</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.2068</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4107</v>
+        <v>1.2935</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.8495</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.6556</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1939</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.2679</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.3073</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.5753</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3501</v>
+        <v>3.016</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5843</v>
+        <v>3.016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7658</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6508</v>
+        <v>3.016</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5512</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09950000000000001</v>
+        <v>2.4107</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5003</v>
+        <v>3.016</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2068</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2935</v>
+        <v>2.4107</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8495</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6556</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1939</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4349</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6366</v>
+        <v>1.7314</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6316</v>
+        <v>1.4737</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005</v>
+        <v>0.2577</v>
       </c>
       <c r="G8" t="n">
         <v>-0.042</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1728</v>
+        <v>-0.078</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2458</v>
+        <v>-0.4037</v>
       </c>
       <c r="U8" t="n">
-        <v>0.073</v>
+        <v>0.3257</v>
       </c>
       <c r="V8" t="n">
         <v>0.0674</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.208</v>
+        <v>1.4099</v>
       </c>
       <c r="E9" t="n">
-        <v>1.208</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.7007</v>
       </c>
       <c r="G9" t="n">
-        <v>1.208</v>
+        <v>-0.3985</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4759</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6027</v>
+        <v>-0.8743</v>
       </c>
       <c r="J9" t="n">
-        <v>1.208</v>
+        <v>0.9156</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.8676</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6027</v>
+        <v>0.048</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.3141</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.3918</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.9223</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4625</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.0348</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.4973</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.5441</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9628</v>
+        <v>1.208</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3183</v>
+        <v>1.208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6445</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3985</v>
+        <v>1.208</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4759</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8743</v>
+        <v>0.6027</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9156</v>
+        <v>1.208</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8676</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.048</v>
+        <v>0.6027</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3141</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3918</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9223</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0154</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4257</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4411</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8874</v>
+        <v>0.9415</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9136</v>
+        <v>0.7677</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0262</v>
+        <v>0.1737</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6543</v>
+        <v>0.1981</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3589</v>
+        <v>0.5999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7046</v>
+        <v>-0.4018</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2817</v>
+        <v>0.6659</v>
       </c>
       <c r="K11" t="n">
-        <v>6.356</v>
+        <v>0.6659</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.0742</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3726</v>
+        <v>-0.4677</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9971</v>
+        <v>-0.066</v>
       </c>
       <c r="O11" t="n">
-        <v>1.3697</v>
+        <v>-0.4018</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7751</v>
+        <v>0.5947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2153</v>
+        <v>0.1487</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3892</v>
+        <v>0.1019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.0468</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7491</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6035</v>
+        <v>-0.6755</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1457</v>
+        <v>1.4836</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1981</v>
+        <v>0.5006</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5999</v>
+        <v>1.067</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4018</v>
+        <v>-0.5664</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6659</v>
+        <v>0.8539</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6659</v>
+        <v>2.5297</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.6758</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4677</v>
+        <v>-0.3533</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.066</v>
+        <v>-1.4627</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4018</v>
+        <v>1.1094</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5947</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0437</v>
+        <v>0.0945</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0624</v>
+        <v>-0.2963</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0187</v>
+        <v>0.3908</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2041</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5362</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. JIMÉNEZ EXPÓSITO</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3027</v>
+        <v>0.5557</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3027</v>
+        <v>0.8346</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.2789</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3027</v>
+        <v>3.6543</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3027</v>
+        <v>5.3589</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-1.7046</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3027</v>
+        <v>3.2817</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3027</v>
+        <v>6.356</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-3.0742</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.3726</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-0.9971</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.3697</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.5734</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. JIMÉNEZ EXPÓSITO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2526</v>
+        <v>0.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2307</v>
+        <v>0.3027</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9781</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5006</v>
+        <v>0.3027</v>
       </c>
       <c r="H14" t="n">
-        <v>1.067</v>
+        <v>0.3027</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5664</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8539</v>
+        <v>0.3027</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5297</v>
+        <v>0.3027</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6758</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3533</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4627</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1094</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9661999999999999</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8515</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1147</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2041</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9599</v>
+        <v>-0.4005</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1446</v>
+        <v>1.5355</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1045</v>
+        <v>-1.936</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4927</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3979</v>
+        <v>0.1615</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4992</v>
+        <v>-0.1082</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1013</v>
+        <v>0.2698</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4658</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LOPEZ PERAGON</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5264</v>
+        <v>-1.0983</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6721</v>
+        <v>-1.422</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1457</v>
+        <v>0.3237</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0863</v>
+        <v>-1.1115</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0054</v>
+        <v>-1.3697</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0809</v>
+        <v>0.2582</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6186</v>
+        <v>-0.1354</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0605</v>
+        <v>0.3027</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6791</v>
+        <v>-0.4381</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4677</v>
+        <v>-0.9761</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.066</v>
+        <v>-1.6723</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4018</v>
+        <v>0.6962</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0437</v>
+        <v>-0.0542</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0624</v>
+        <v>-0.2954</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0187</v>
+        <v>0.2412</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>M. LOPEZ PERAGON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7419</v>
+        <v>-1.3341</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8129</v>
+        <v>-1.5078</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1737</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1115</v>
+        <v>-1.0863</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3697</v>
+        <v>-0.0054</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2582</v>
+        <v>-1.0809</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1354</v>
+        <v>-0.6186</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3027</v>
+        <v>0.0605</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4381</v>
+        <v>-0.6791</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9761</v>
+        <v>-0.4677</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6723</v>
+        <v>-0.066</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6962</v>
+        <v>-0.4018</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6978</v>
+        <v>0.1487</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6864</v>
+        <v>0.1019</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0115</v>
+        <v>0.0468</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>33.68819999999999</v>
+        <v>35.8721</v>
       </c>
       <c r="E18" t="n">
-        <v>27.7068</v>
+        <v>29.8906</v>
       </c>
       <c r="F18" t="n">
-        <v>5.9815</v>
+        <v>5.9814</v>
       </c>
       <c r="G18" t="n">
         <v>26.6037</v>
@@ -1828,7 +1828,7 @@
         <v>18.5683</v>
       </c>
       <c r="I18" t="n">
-        <v>8.035500000000001</v>
+        <v>8.035499999999999</v>
       </c>
       <c r="J18" t="n">
         <v>35.9975</v>
@@ -1837,10 +1837,10 @@
         <v>27.5107</v>
       </c>
       <c r="L18" t="n">
-        <v>8.486800000000001</v>
+        <v>8.486799999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-9.393699999999999</v>
+        <v>-9.393700000000001</v>
       </c>
       <c r="N18" t="n">
         <v>-8.942799999999998</v>
@@ -1858,19 +1858,19 @@
         <v>18.8312</v>
       </c>
       <c r="S18" t="n">
-        <v>2.128800000000001</v>
+        <v>4.3127</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.9906</v>
+        <v>-0.8064</v>
       </c>
       <c r="U18" t="n">
-        <v>5.119299999999999</v>
+        <v>5.1195</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5756</v>
+        <v>8.575600000000001</v>
       </c>
       <c r="X18" t="n">
         <v>-8.575699999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7963</v>
+        <v>1.158</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3701</v>
+        <v>2.2683</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5739</v>
+        <v>-1.1102</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2287</v>
@@ -1936,13 +1936,13 @@
         <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3369</v>
+        <v>0.0248</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4954</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1584</v>
+        <v>0.6221</v>
       </c>
       <c r="V19" t="n">
         <v>3.1636</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1406</v>
+        <v>0.1687</v>
       </c>
       <c r="E20" t="n">
         <v>1.002</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.8334</v>
       </c>
       <c r="G20" t="n">
         <v>0.1843</v>
@@ -2014,13 +2014,13 @@
         <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2419</v>
+        <v>-0.2138</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0547</v>
+        <v>-0.0266</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2257</v>
+        <v>-0.6367</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6476</v>
+        <v>1.157</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8734</v>
+        <v>-1.7937</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6184</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3825</v>
+        <v>0.2065</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1855</v>
+        <v>-0.6762</v>
       </c>
       <c r="U21" t="n">
-        <v>0.803</v>
+        <v>0.8827</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MARTOS BONACHELA</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2863</v>
+        <v>-1.575</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0707</v>
+        <v>-0.4445</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2156</v>
+        <v>-1.1305</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0578</v>
+        <v>-1.247</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8878</v>
+        <v>0.1304</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9456</v>
+        <v>-1.3774</v>
       </c>
       <c r="J22" t="n">
-        <v>2.6603</v>
+        <v>2.545</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9371</v>
+        <v>2.6098</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7232</v>
+        <v>-0.0648</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6024</v>
+        <v>-3.7921</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.8249</v>
+        <v>-2.4794</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2224</v>
+        <v>-1.3126</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5769</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9733</v>
+        <v>-3.1716</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2328</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2423</v>
+        <v>-0.6881</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.5909</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.1568</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>A. MARTOS BONACHELA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5702</v>
+        <v>-1.5815</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0557</v>
+        <v>-0.4782</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5145</v>
+        <v>-1.1033</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.247</v>
+        <v>1.0578</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1304</v>
+        <v>-0.8878</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3774</v>
+        <v>1.9456</v>
       </c>
       <c r="J23" t="n">
-        <v>2.545</v>
+        <v>2.6603</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6098</v>
+        <v>1.9371</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0648</v>
+        <v>0.7232</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.7921</v>
+        <v>-1.6024</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.4794</v>
+        <v>-2.8249</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3126</v>
+        <v>1.2224</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3876</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1716</v>
+        <v>-2.9733</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0924</v>
+        <v>-0.0624</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2993</v>
+        <v>-0.1651</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2069</v>
+        <v>0.1027</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1568</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8675</v>
+        <v>-2.8269</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3824</v>
+        <v>-1.3151</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4851</v>
+        <v>-1.5118</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3095</v>
+        <v>-2.119</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3662</v>
+        <v>-0.3647</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9433</v>
+        <v>-1.7543</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4375</v>
+        <v>-1.2574</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1211</v>
+        <v>0.1009</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5586</v>
+        <v>-1.3583</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8719</v>
+        <v>-0.8617</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4873</v>
+        <v>-0.4656</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3847</v>
+        <v>-0.3961</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1526</v>
+        <v>0.1028</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0552</v>
+        <v>-0.0577</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2078</v>
+        <v>0.1606</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="25">
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2729</v>
+        <v>-3.0607</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6207</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6521</v>
+        <v>-2.3728</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.119</v>
+        <v>-3.3095</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3647</v>
+        <v>-2.3662</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.7543</v>
+        <v>-0.9433</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2574</v>
+        <v>-0.4375</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1009</v>
+        <v>0.1211</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3583</v>
+        <v>-0.5586</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8617</v>
+        <v>-2.8719</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4656</v>
+        <v>-2.4873</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3961</v>
+        <v>-0.3847</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3432</v>
+        <v>-0.3459</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3634</v>
+        <v>-0.2505</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0202</v>
+        <v>-0.0955</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.9657</v>
+        <v>-4.3868</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2648</v>
+        <v>-0.6723</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.7009</v>
+        <v>-3.7146</v>
       </c>
       <c r="G27" t="n">
         <v>-3.1449</v>
@@ -2560,13 +2560,13 @@
         <v>1.9822</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4387</v>
+        <v>0.0175</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0589</v>
+        <v>-0.3485</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3797</v>
+        <v>0.366</v>
       </c>
       <c r="V27" t="n">
         <v>-1.0612</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.1518</v>
+        <v>-4.7502</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.5867</v>
+        <v>-3.4848</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.5651</v>
+        <v>-1.2653</v>
       </c>
       <c r="G28" t="n">
         <v>-4.0347</v>
@@ -2638,13 +2638,13 @@
         <v>1.1893</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.112</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5616</v>
+        <v>-0.4597</v>
       </c>
       <c r="U28" t="n">
-        <v>0.048</v>
+        <v>0.3478</v>
       </c>
       <c r="V28" t="n">
         <v>-0.6036</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.4803</v>
+        <v>-5.4895</v>
       </c>
       <c r="E29" t="n">
         <v>-2.8193</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.661</v>
+        <v>-2.6702</v>
       </c>
       <c r="G29" t="n">
         <v>-7.5934</v>
@@ -2716,13 +2716,13 @@
         <v>1.3876</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3964</v>
+        <v>0.3873</v>
       </c>
       <c r="T29" t="n">
         <v>-0.745</v>
       </c>
       <c r="U29" t="n">
-        <v>1.1414</v>
+        <v>1.1323</v>
       </c>
       <c r="V29" t="n">
         <v>3.5006</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-5.9294</v>
+        <v>-5.7949</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8548</v>
+        <v>0.5491</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.7841</v>
+        <v>-6.344</v>
       </c>
       <c r="G30" t="n">
         <v>-1.8734</v>
@@ -2794,13 +2794,13 @@
         <v>1.5858</v>
       </c>
       <c r="S30" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1993</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.5137</v>
+        <v>-0.8193</v>
       </c>
       <c r="U30" t="n">
-        <v>0.5784</v>
+        <v>1.0185</v>
       </c>
       <c r="V30" t="n">
         <v>-2.5349</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-33.688</v>
+        <v>-31.6506</v>
       </c>
       <c r="E31" t="n">
-        <v>-5.981400000000001</v>
+        <v>-5.9814</v>
       </c>
       <c r="F31" t="n">
-        <v>-27.7066</v>
+        <v>-25.6693</v>
       </c>
       <c r="G31" t="n">
         <v>-26.6038</v>
@@ -2860,7 +2860,7 @@
         <v>-27.5107</v>
       </c>
       <c r="O31" t="n">
-        <v>-8.486600000000001</v>
+        <v>-8.486599999999999</v>
       </c>
       <c r="P31" t="n">
         <v>-4.9557</v>
@@ -2872,13 +2872,13 @@
         <v>13.8755</v>
       </c>
       <c r="S31" t="n">
-        <v>-2.1287</v>
+        <v>-0.09130000000000008</v>
       </c>
       <c r="T31" t="n">
-        <v>-5.119499999999999</v>
+        <v>-5.119400000000001</v>
       </c>
       <c r="U31" t="n">
-        <v>2.9905</v>
+        <v>5.0281</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
